--- a/InputData/indst/_cement/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
+++ b/InputData/indst/_cement/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CNBEIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D6D431-6923-48B2-9B5C-10E87450888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B08D50B-6CF1-47EB-B840-05445555A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -74,12 +74,6 @@
     <t>Fleet-typical thermal energy intensity (MMBtu/metric ton; matches CEIbPaF convention)</t>
   </si>
   <si>
-    <t>Precalciner CNBEIR (unrounded) = BAT (GJ/t, converted to MMBtu at 1.05506 GJ per MMBtu) / fleet-typical (MMBtu/t)</t>
-  </si>
-  <si>
-    <t>Precalciner CNBEIR (rounded to 3 decimal places)</t>
-  </si>
-  <si>
     <t>CEIbPaF precalciner pathway fuel total (BTU/metric ton clinker)</t>
   </si>
   <si>
@@ -93,12 +87,6 @@
   </si>
   <si>
     <t>BAT credit on the amine adder (1.0 = no discount; process energy, not kiln pyroprocessing)</t>
-  </si>
-  <si>
-    <t>CCS CNBEIR (unrounded) = (precalciner CNBEIR x kiln component + 1.0 x amine adder) / CCS total</t>
-  </si>
-  <si>
-    <t>CCS CNBEIR (rounded to 3 decimal places)</t>
   </si>
   <si>
     <t>Electric kiln</t>
@@ -165,9 +153,6 @@
 The tabs run from inputs to output. 'Derivation' holds the DOE figures, the arithmetic, and the judgment values for the electric kiln and alternative chemistry. 'Checks' tests that each ratio sits between 0.5 and 1.0. The 'CNBEIR' tab reads from 'Derivation' by formula, repeats each pathway's value across 2021-2050, and is what gets exported to CNBEIR.csv.</t>
   </si>
   <si>
-    <t>The ratio is the best-available energy intensity over the fleet-typical intensity. We convert the DOE best-practice figure from 2.9 GJ to 2.75 million BTU per metric ton of clinker (dividing by 1.05506 GJ per million BTU) and divide by the fleet-typical 3.426 million BTU per metric ton. The result, 0.802, is rounded to three decimal places. In plain terms, a new best-practice kiln uses about 20% less thermal energy per ton of clinker than the current U.S. average.</t>
-  </si>
-  <si>
     <t>Dry kiln with CCS</t>
   </si>
   <si>
@@ -193,6 +178,21 @@
   </si>
   <si>
     <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Precalciner CNBEIR = BAT (GJ/t, converted to MMBtu at 1.05506 GJ per MMBtu) / fleet-typical (MMBtu/t)</t>
+  </si>
+  <si>
+    <t>Precalciner CNBEIR (value used)</t>
+  </si>
+  <si>
+    <t>CCS CNBEIR = precalciner value (the CEIbPaF CCS row is kiln only)</t>
+  </si>
+  <si>
+    <t>CCS CNBEIR (value used)</t>
+  </si>
+  <si>
+    <t>The ratio is the best-available energy intensity over the fleet-typical intensity. We convert the DOE best-practice figure from 2.9 GJ to 2.75 million BTU per metric ton of clinker (dividing by 1.05506 GJ per million BTU) and divide by the fleet-typical 3.426 million BTU per metric ton. The result is 0.8023. In plain terms, a new best-practice kiln uses about 20% less thermal energy per ton of clinker than the current U.S. average.</t>
   </si>
 </sst>
 </file>
@@ -278,10 +278,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,130 +588,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="7">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B23" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{9559D2AB-B0DB-4162-843A-0CBA7ADD2D49}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{FF2300C1-FB73-490F-96E2-127203A1E4A2}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{5ADBD711-3BD0-4B2A-91B4-51CA4994478B}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{73EE4595-6DE3-466B-B747-63FFB0948FF0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -720,19 +721,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -740,7 +741,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -748,7 +749,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -756,7 +757,7 @@
         <v>2204.62</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -765,118 +766,118 @@
         <v>3.4259794800000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B8">
         <f>B4/1.05506/B7</f>
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1">
-        <f>ROUND(B8,3)</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <f>(B8)</f>
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>4020000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>6270000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <f>B13-B12</f>
         <v>2250000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <f>B9</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <f>B9</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1">
-        <f>ROUND(B17,3)</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <f>(B17)</f>
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -887,47 +888,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B3" t="str">
         <f>IF(AND(MIN(CNBEIR!B2:AE2)&gt;=0.5,MAX(CNBEIR!B2:AE2)&lt;=1),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B4" t="str">
         <f>IF(AND(MIN(CNBEIR!B3:AE3)&gt;=0.5,MAX(CNBEIR!B3:AE3)&lt;=1),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B5" t="str">
         <f>IF(AND(MIN(CNBEIR!B4:AE4)&gt;=0.5,MAX(CNBEIR!B4:AE4)&lt;=1),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B6" t="str">
         <f>IF(AND(MIN(CNBEIR!B5:AE5)&gt;=0.5,MAX(CNBEIR!B5:AE5)&lt;=1),"PASS","FAIL")</f>
@@ -945,11 +946,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1042,259 +1043,259 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="C2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="D2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="E2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="F2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="G2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="H2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="I2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="J2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="K2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="L2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="M2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="N2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="O2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="P2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Q2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="R2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="S2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="T2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="U2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="V2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="W2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="X2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Y2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Z2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AA2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AB2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AC2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AD2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AE2">
         <f>Derivation!$B$9</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="C3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="D3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="E3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="F3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="G3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="H3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="I3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="J3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="K3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="L3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="M3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="N3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="O3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="P3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Q3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="R3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="S3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="T3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="U3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="V3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="W3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="X3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Y3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="Z3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AA3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AB3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AC3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AD3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
+        <v>0.80229868862109577</v>
       </c>
       <c r="AE3">
         <f>Derivation!$B$18</f>
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.80229868862109577</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <f>Derivation!$B$21</f>
@@ -1417,9 +1418,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <f>Derivation!$B$24</f>

--- a/InputData/indst/_cement/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
+++ b/InputData/indst/_cement/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CNBEIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B08D50B-6CF1-47EB-B840-05445555A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE689EBC-1A72-477E-A4E0-2B2D87965169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>CNBEIR Cement New Build Energy Intensity Ratio</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>The ratio is the best-available energy intensity over the fleet-typical intensity. We convert the DOE best-practice figure from 2.9 GJ to 2.75 million BTU per metric ton of clinker (dividing by 1.05506 GJ per million BTU) and divide by the fleet-typical 3.426 million BTU per metric ton. The result is 0.8023. In plain terms, a new best-practice kiln uses about 20% less thermal energy per ton of clinker than the current U.S. average.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
@@ -265,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -281,8 +290,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -587,21 +602,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -609,67 +624,67 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -677,7 +692,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
@@ -685,7 +700,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -693,7 +708,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -701,12 +716,20 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -721,19 +744,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -741,7 +764,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -749,7 +772,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -757,7 +780,7 @@
         <v>2204.62</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -766,7 +789,7 @@
         <v>3.4259794800000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -775,7 +798,7 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -784,12 +807,12 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -797,7 +820,7 @@
         <v>4020000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -805,7 +828,7 @@
         <v>6270000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -814,7 +837,7 @@
         <v>2250000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -823,7 +846,7 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -831,7 +854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -840,7 +863,7 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>50</v>
       </c>
@@ -849,12 +872,12 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -862,12 +885,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -875,7 +898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
@@ -888,18 +911,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="70.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -908,7 +931,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -917,7 +940,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -926,12 +949,12 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
       <c r="B6" t="str">
-        <f>IF(AND(MIN(CNBEIR!B5:AE5)&gt;=0.5,MAX(CNBEIR!B5:AE5)&lt;=1),"PASS","FAIL")</f>
+        <f>IF(AND(MIN(CNBEIR!B6:AE6)&gt;=0.5,MAX(CNBEIR!B6:AE6)&lt;=1),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -945,10 +968,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -1043,7 +1066,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1168,7 +1191,7 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1293,7 +1316,7 @@
         <v>0.80229868862109577</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1418,127 +1441,252 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>C4</f>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>D4</f>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>E4</f>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <f>F4</f>
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <f>G4</f>
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <f>H4</f>
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <f>I4</f>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <f>J4</f>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <f>K4</f>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f>L4</f>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <f>M4</f>
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <f>N4</f>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f>O4</f>
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <f>P4</f>
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <f>Q4</f>
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <f>R4</f>
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <f>S4</f>
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <f>T4</f>
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <f>U4</f>
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <f>V4</f>
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <f>W4</f>
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <f>X4</f>
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <f>Y4</f>
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <f>Z4</f>
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <f>AA4</f>
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <f>AB4</f>
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <f>AC4</f>
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <f>AD4</f>
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <f>AE4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="X5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="Z5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <f>Derivation!$B$24</f>
-        <v>1</v>
-      </c>
-      <c r="AE5">
+      <c r="B6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <f>Derivation!$B$24</f>
+        <v>1</v>
+      </c>
+      <c r="AE6">
         <f>Derivation!$B$24</f>
         <v>1</v>
       </c>
